--- a/审核导出/00_汇总清单.xlsx
+++ b/审核导出/00_汇总清单.xlsx
@@ -803,7 +803,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>6470</v>
